--- a/templates/Grafik-dane-2026-08.xlsx
+++ b/templates/Grafik-dane-2026-08.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Instrukcja" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Pracownicy" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Dostępność" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Administrator" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -452,24 +453,39 @@
         <t>Czy bierzesz dyżury 24-godzinne i w jakim układzie.</t>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0">
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Grafik</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0">
       <text>
-        <t>Twoje kwalifikacje, po przecinku. Domyślnie: General.</t>
+        <t>Musi brzmieć tak samo jak w zakładce Pracownicy.</t>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0">
+    <comment ref="B3" authorId="0" shapeId="0">
       <text>
-        <t>Tak, jeśli możesz pełnić zmianę kierownika.</t>
+        <t>Kwalifikacje, po przecinku. Puste = General.</t>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Tak, jeśli ta osoba może pełnić zmianę kierownika.</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Tak tylko dla jednej osoby w zespole.</t>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0">
+    <comment ref="E3" authorId="0" shapeId="0">
       <text>
-        <t>Pole dowolne — program je pomija.</t>
+        <t>Notatki osoby układającej grafik — program je pomija.</t>
       </text>
     </comment>
   </commentList>
@@ -766,7 +782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -841,67 +857,67 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
     </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" s="6" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Zakładka „Administrator”</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Należy do osoby układającej grafik: kwalifikacje, uprawnienia kierownika i notatki. Arkusz jest chroniony — pracownicy go nie zmieniają.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="8" customHeight="1">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Kody dostępności</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>niedostępny przez cały dzień (urlop, L4)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>niedostępny rano i w dzień — noce są w porządku</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>niedostępny w nocy — dni są w porządku</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>puste pole — jestem dostępny</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="8" customHeight="1">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>O czym pamiętać</t>
         </is>
       </c>
     </row>
@@ -909,49 +925,69 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
+          <t>puste pole — jestem dostępny</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="8" customHeight="1">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>O czym pamiętać</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
           <t>Imię i nazwisko musi brzmieć tak samo w obu zakładkach — w „Dostępności” wybierz je z listy.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Nie zmieniaj nazw zakładek ani nagłówków kolumn — po nich program rozpoznaje dane.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Możesz dopisywać wiersze na dole i dodawać własne kolumny; program pomija to, czego nie zna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="8" customHeight="1">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Dla osoby układającej grafik</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
+          <t>Możesz dopisywać wiersze na dole i dodawać własne kolumny; program pomija to, czego nie zna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="8" customHeight="1">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Dla osoby układającej grafik</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
           <t>Gdy zespół skończy: Plik → Pobierz → Microsoft Excel (.xlsx), a następnie w programie Shiftwise zakładka Workers → Import from sheet. Przed zapisem zobaczysz podgląd wszystkich zmian.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" s="11" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Miesiąc, którego dotyczy arkusz, jest w komórce B1 zakładki „Dostępność”. Aby użyć tego samego arkusza w kolejnym miesiącu, zmień tę komórkę i wyczyść siatkę.</t>
         </is>
@@ -969,17 +1005,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -992,7 +1024,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>Jeden wiersz na osobę · sierpień 2026</t>
+          <t>Jeden wiersz na osobę · sierpień 2026 · wypełniają pracownicy</t>
         </is>
       </c>
     </row>
@@ -1015,26 +1047,6 @@
       <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Dyżur 24h</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>Kategorie</t>
-        </is>
-      </c>
-      <c r="F3" s="14" t="inlineStr">
-        <is>
-          <t>Uprawnienia kierownika</t>
-        </is>
-      </c>
-      <c r="G3" s="14" t="inlineStr">
-        <is>
-          <t>Kierownik domyślny</t>
-        </is>
-      </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t>Uwagi</t>
         </is>
       </c>
     </row>
@@ -1043,314 +1055,188 @@
       <c r="B4" s="16" t="n"/>
       <c r="C4" s="17" t="n"/>
       <c r="D4" s="17" t="n"/>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="17" t="n"/>
-      <c r="G4" s="17" t="n"/>
-      <c r="H4" s="15" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="18" t="n"/>
       <c r="B5" s="19" t="n"/>
       <c r="C5" s="20" t="n"/>
       <c r="D5" s="20" t="n"/>
-      <c r="E5" s="18" t="n"/>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="20" t="n"/>
-      <c r="H5" s="18" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="15" t="n"/>
       <c r="B6" s="16" t="n"/>
       <c r="C6" s="17" t="n"/>
       <c r="D6" s="17" t="n"/>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="17" t="n"/>
-      <c r="G6" s="17" t="n"/>
-      <c r="H6" s="15" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="18" t="n"/>
       <c r="B7" s="19" t="n"/>
       <c r="C7" s="20" t="n"/>
       <c r="D7" s="20" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="18" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="15" t="n"/>
       <c r="B8" s="16" t="n"/>
       <c r="C8" s="17" t="n"/>
       <c r="D8" s="17" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="15" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="18" t="n"/>
       <c r="B9" s="19" t="n"/>
       <c r="C9" s="20" t="n"/>
       <c r="D9" s="20" t="n"/>
-      <c r="E9" s="18" t="n"/>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="18" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="15" t="n"/>
       <c r="B10" s="16" t="n"/>
       <c r="C10" s="17" t="n"/>
       <c r="D10" s="17" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="17" t="n"/>
-      <c r="H10" s="15" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="18" t="n"/>
       <c r="B11" s="19" t="n"/>
       <c r="C11" s="20" t="n"/>
       <c r="D11" s="20" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="18" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="15" t="n"/>
       <c r="B12" s="16" t="n"/>
       <c r="C12" s="17" t="n"/>
       <c r="D12" s="17" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="17" t="n"/>
-      <c r="H12" s="15" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="18" t="n"/>
       <c r="B13" s="19" t="n"/>
       <c r="C13" s="20" t="n"/>
       <c r="D13" s="20" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="18" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="15" t="n"/>
       <c r="B14" s="16" t="n"/>
       <c r="C14" s="17" t="n"/>
       <c r="D14" s="17" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="17" t="n"/>
-      <c r="H14" s="15" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="18" t="n"/>
       <c r="B15" s="19" t="n"/>
       <c r="C15" s="20" t="n"/>
       <c r="D15" s="20" t="n"/>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="18" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="15" t="n"/>
       <c r="B16" s="16" t="n"/>
       <c r="C16" s="17" t="n"/>
       <c r="D16" s="17" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="17" t="n"/>
-      <c r="G16" s="17" t="n"/>
-      <c r="H16" s="15" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="18" t="n"/>
       <c r="B17" s="19" t="n"/>
       <c r="C17" s="20" t="n"/>
       <c r="D17" s="20" t="n"/>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="20" t="n"/>
-      <c r="G17" s="20" t="n"/>
-      <c r="H17" s="18" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="15" t="n"/>
       <c r="B18" s="16" t="n"/>
       <c r="C18" s="17" t="n"/>
       <c r="D18" s="17" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="17" t="n"/>
-      <c r="G18" s="17" t="n"/>
-      <c r="H18" s="15" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="18" t="n"/>
       <c r="B19" s="19" t="n"/>
       <c r="C19" s="20" t="n"/>
       <c r="D19" s="20" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="20" t="n"/>
-      <c r="G19" s="20" t="n"/>
-      <c r="H19" s="18" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="15" t="n"/>
       <c r="B20" s="16" t="n"/>
       <c r="C20" s="17" t="n"/>
       <c r="D20" s="17" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="17" t="n"/>
-      <c r="G20" s="17" t="n"/>
-      <c r="H20" s="15" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="18" t="n"/>
       <c r="B21" s="19" t="n"/>
       <c r="C21" s="20" t="n"/>
       <c r="D21" s="20" t="n"/>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="20" t="n"/>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="18" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="15" t="n"/>
       <c r="B22" s="16" t="n"/>
       <c r="C22" s="17" t="n"/>
       <c r="D22" s="17" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="15" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="18" t="n"/>
       <c r="B23" s="19" t="n"/>
       <c r="C23" s="20" t="n"/>
       <c r="D23" s="20" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="20" t="n"/>
-      <c r="G23" s="20" t="n"/>
-      <c r="H23" s="18" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="15" t="n"/>
       <c r="B24" s="16" t="n"/>
       <c r="C24" s="17" t="n"/>
       <c r="D24" s="17" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="17" t="n"/>
-      <c r="G24" s="17" t="n"/>
-      <c r="H24" s="15" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="18" t="n"/>
       <c r="B25" s="19" t="n"/>
       <c r="C25" s="20" t="n"/>
       <c r="D25" s="20" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="20" t="n"/>
-      <c r="G25" s="20" t="n"/>
-      <c r="H25" s="18" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="15" t="n"/>
       <c r="B26" s="16" t="n"/>
       <c r="C26" s="17" t="n"/>
       <c r="D26" s="17" t="n"/>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="15" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="18" t="n"/>
       <c r="B27" s="19" t="n"/>
       <c r="C27" s="20" t="n"/>
       <c r="D27" s="20" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="20" t="n"/>
-      <c r="G27" s="20" t="n"/>
-      <c r="H27" s="18" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="15" t="n"/>
       <c r="B28" s="16" t="n"/>
       <c r="C28" s="17" t="n"/>
       <c r="D28" s="17" t="n"/>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="17" t="n"/>
-      <c r="G28" s="17" t="n"/>
-      <c r="H28" s="15" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="18" t="n"/>
       <c r="B29" s="19" t="n"/>
       <c r="C29" s="20" t="n"/>
       <c r="D29" s="20" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="20" t="n"/>
-      <c r="G29" s="20" t="n"/>
-      <c r="H29" s="18" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="15" t="n"/>
       <c r="B30" s="16" t="n"/>
       <c r="C30" s="17" t="n"/>
       <c r="D30" s="17" t="n"/>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="17" t="n"/>
-      <c r="G30" s="17" t="n"/>
-      <c r="H30" s="15" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="18" t="n"/>
       <c r="B31" s="19" t="n"/>
       <c r="C31" s="20" t="n"/>
       <c r="D31" s="20" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="20" t="n"/>
-      <c r="G31" s="20" t="n"/>
-      <c r="H31" s="18" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="15" t="n"/>
       <c r="B32" s="16" t="n"/>
       <c r="C32" s="17" t="n"/>
       <c r="D32" s="17" t="n"/>
-      <c r="E32" s="15" t="n"/>
-      <c r="F32" s="17" t="n"/>
-      <c r="G32" s="17" t="n"/>
-      <c r="H32" s="15" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="18" t="n"/>
       <c r="B33" s="19" t="n"/>
       <c r="C33" s="20" t="n"/>
       <c r="D33" s="20" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="20" t="n"/>
-      <c r="G33" s="20" t="n"/>
-      <c r="H33" s="18" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="3">
     <dataValidation sqref="C4:C33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Preferowana pora" error="Wybierz: Dzień, Noc albo Bez preferencji." promptTitle="Preferowana pora" prompt="Wybierz: Dzień, Noc albo Bez preferencji." type="list">
       <formula1>"Dzień,Noc,Bez preferencji"</formula1>
     </dataValidation>
     <dataValidation sqref="D4:D33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Dyżur 24h" error="Nie, Dowolny albo konkretny układ 24-godzinny." promptTitle="Dyżur 24h" prompt="Nie, Dowolny albo konkretny układ 24-godzinny." type="list">
       <formula1>"Nie,Dowolny,08:00 → 08:00,20:00 → 20:00"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F4:F33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Uprawnienia kierownika" error="Tak albo Nie." promptTitle="Uprawnienia kierownika" prompt="Tak albo Nie." type="list">
-      <formula1>"Tak,Nie"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G4:G33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Kierownik domyślny" error="Tak tylko dla jednej osoby w zespole." promptTitle="Kierownik domyślny" prompt="Tak tylko dla jednej osoby w zespole." type="list">
-      <formula1>"Tak,Nie"</formula1>
     </dataValidation>
     <dataValidation sqref="B4:B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Godziny docelowe" error="Podaj liczbę godzin z zakresu 0–400." promptTitle="Godziny docelowe" prompt="Ile godzin chcesz przepracować w tym miesiącu." type="whole" operator="between">
       <formula1>0</formula1>
@@ -2894,4 +2780,290 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="006B7A72"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Kwalifikacje i role kierownika · sierpień 2026 · wypełnia osoba układająca grafik</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Imię i nazwisko</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Kategorie</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Uprawnienia kierownika</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Kierownik domyślny</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Uwagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="n"/>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="15" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="18" t="n"/>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="18" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="15" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="18" t="n"/>
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="18" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="15" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="18" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="18" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="18" t="n"/>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="18" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="15" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="18" t="n"/>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="18" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="15" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="18" t="n"/>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="18" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="15" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="18" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="18" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="18" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="18" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="18" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="18" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="18" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="18" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="18" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="15" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="18" t="n"/>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="18" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="15" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="18" t="n"/>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="18" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="15" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="18" t="n"/>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="18" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="15" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="15" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="18" t="n"/>
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <dataValidations count="3">
+    <dataValidation sqref="C4:C33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Tak albo Nie" error="Wpisz Tak albo Nie." type="list">
+      <formula1>"Tak,Nie"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D4:D33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Tak albo Nie" error="Wpisz Tak albo Nie." type="list">
+      <formula1>"Tak,Nie"</formula1>
+    </dataValidation>
+    <dataValidation sqref="A4:A33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Imię i nazwisko" prompt="Wybierz osobę z zakładki Pracownicy." type="list">
+      <formula1>=Pracownicy!$A$4:$A$33</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>